--- a/outputs/etf_trend_strategy/threshold_0.7/backtests/window_40/return_r2/post_rank_positive_return/rebalance_1d/close/close_annual_metrics.xlsx
+++ b/outputs/etf_trend_strategy/threshold_0.7/backtests/window_40/return_r2/post_rank_positive_return/rebalance_1d/close/close_annual_metrics.xlsx
@@ -466,10 +466,10 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
     <col width="21" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="23" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="22" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
@@ -524,25 +524,25 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>0.07492128269290776</v>
+        <v>0.01121639567582489</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>0.3407197515507874</v>
+        <v>0.1917336111177081</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>0.3658268105880336</v>
+        <v>0.083562631580893</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>0.5192906942164114</v>
+        <v>0.1183533526623864</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0.2151054613631378</v>
+        <v>0.1519793857320898</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>0.3954720476811343</v>
+        <v>0.08346029454503104</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>36.44277394565512</v>
+        <v>37.14051534618454</v>
       </c>
     </row>
     <row r="3">
@@ -552,25 +552,25 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>-0.3250784721290874</v>
+        <v>-0.03706315593045206</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>0.2562386550814687</v>
+        <v>0.2845222835456708</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>-1.526627511698851</v>
+        <v>-0.04908313571338819</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>-1.999990384730121</v>
+        <v>-0.07065447640503895</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.4163867255849418</v>
+        <v>0.1885986532312312</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>-0.8068336360543384</v>
+        <v>-0.2044806764799272</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>46.85351149252261</v>
+        <v>20.73116901013445</v>
       </c>
     </row>
     <row r="4">
@@ -580,25 +580,25 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>0.04414858057043758</v>
+        <v>-0.1135750867107014</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>0.2382890797436508</v>
+        <v>0.2475925548706105</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>0.2447003392659695</v>
+        <v>-0.4432642705731646</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>0.3618270478102142</v>
+        <v>-0.5958255892282774</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0.1846027657520851</v>
+        <v>0.2289298417458617</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>0.2492609328914403</v>
+        <v>-0.5153547055301394</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>41.41061339080367</v>
+        <v>46.56065077400039</v>
       </c>
     </row>
     <row r="5">
@@ -608,25 +608,25 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>0.05281984952113272</v>
+        <v>0.5223241766579059</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>0.2404257952824703</v>
+        <v>0.3249142813647232</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>0.2796883080167184</v>
+        <v>1.461440015625011</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>0.4323026900925515</v>
+        <v>2.512142307613254</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>0.1951623863446322</v>
+        <v>0.1464098247536924</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>0.2821318517179577</v>
+        <v>3.749683665872943</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>44.65210562577559</v>
+        <v>39.21648758132584</v>
       </c>
     </row>
     <row r="6">
@@ -636,25 +636,25 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>0.2695549381220088</v>
+        <v>0.2659242178870471</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>0.2752793704462895</v>
+        <v>0.3103651539829483</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>0.9835506985109792</v>
+        <v>0.8959315123234022</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>1.37790812983209</v>
+        <v>1.253735282930256</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0.2352130050928199</v>
+        <v>0.2476719384154766</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>1.193925947700782</v>
+        <v>1.118529987149572</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>52.76747259737189</v>
+        <v>40.59753986105895</v>
       </c>
     </row>
     <row r="7">
@@ -664,25 +664,25 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>-0.02738184947589972</v>
+        <v>0.4653673319418787</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.3463320161762919</v>
+        <v>0.4225272681997226</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-0.01557498363889642</v>
+        <v>1.814973833662824</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-0.02144913539350415</v>
+        <v>2.914271636600278</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.2505149645005652</v>
+        <v>0.1770919010454052</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-0.1959501584976574</v>
+        <v>5.642174979961739</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>31.86800434208214</v>
+        <v>37.29620139799994</v>
       </c>
     </row>
   </sheetData>
